--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121745446</v>
+        <v>121744535</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -829,29 +829,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626770</v>
+        <v>626787</v>
       </c>
       <c r="R3" t="n">
-        <v>6706680</v>
+        <v>6706309</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121744535</v>
+        <v>121745229</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -947,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626787</v>
+        <v>626755</v>
       </c>
       <c r="R4" t="n">
-        <v>6706309</v>
+        <v>6706575</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121745229</v>
+        <v>121745446</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1042,17 +1033,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626755</v>
+        <v>626770</v>
       </c>
       <c r="R5" t="n">
-        <v>6706575</v>
+        <v>6706680</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121744535</v>
+        <v>121745229</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626787</v>
+        <v>626755</v>
       </c>
       <c r="R3" t="n">
-        <v>6706309</v>
+        <v>6706575</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121745229</v>
+        <v>121745446</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -931,17 +931,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626755</v>
+        <v>626770</v>
       </c>
       <c r="R4" t="n">
-        <v>6706575</v>
+        <v>6706680</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121745446</v>
+        <v>121744535</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1033,29 +1042,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626770</v>
+        <v>626787</v>
       </c>
       <c r="R5" t="n">
-        <v>6706680</v>
+        <v>6706309</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121745229</v>
+        <v>121744535</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626755</v>
+        <v>626787</v>
       </c>
       <c r="R3" t="n">
-        <v>6706575</v>
+        <v>6706309</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121745446</v>
+        <v>121745229</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -931,26 +931,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626770</v>
+        <v>626755</v>
       </c>
       <c r="R4" t="n">
-        <v>6706680</v>
+        <v>6706575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121744535</v>
+        <v>121745446</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1042,20 +1033,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bondmuren, Bondmuren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626787</v>
+        <v>626770</v>
       </c>
       <c r="R5" t="n">
-        <v>6706309</v>
+        <v>6706680</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,6 +1109,482 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121974044</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98113</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Båtfors norr om reservatet, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>626770</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6706475</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121974046</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98113</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Båtfors norr om reservatet, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>626774</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6706525</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121974043</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98113</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Båtfors norr om reservatet, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>626822</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6706382</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121974045</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98113</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Båtfors norr om reservatet, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626774</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6706491</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121744535</v>
+        <v>121745229</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626787</v>
+        <v>626755</v>
       </c>
       <c r="R3" t="n">
-        <v>6706309</v>
+        <v>6706575</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121745229</v>
+        <v>121744535</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626755</v>
+        <v>626787</v>
       </c>
       <c r="R4" t="n">
-        <v>6706575</v>
+        <v>6706309</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121974044</v>
+        <v>121974045</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626770</v>
+        <v>626774</v>
       </c>
       <c r="R6" t="n">
-        <v>6706475</v>
+        <v>6706491</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121974046</v>
+        <v>121974044</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626774</v>
+        <v>626770</v>
       </c>
       <c r="R7" t="n">
-        <v>6706525</v>
+        <v>6706475</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121974043</v>
+        <v>121974046</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626822</v>
+        <v>626774</v>
       </c>
       <c r="R8" t="n">
-        <v>6706382</v>
+        <v>6706525</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1468,7 +1468,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121974045</v>
+        <v>121974043</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626774</v>
+        <v>626822</v>
       </c>
       <c r="R9" t="n">
-        <v>6706491</v>
+        <v>6706382</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121745229</v>
+        <v>121744535</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626755</v>
+        <v>626787</v>
       </c>
       <c r="R3" t="n">
-        <v>6706575</v>
+        <v>6706309</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121744535</v>
+        <v>121745229</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626787</v>
+        <v>626755</v>
       </c>
       <c r="R4" t="n">
-        <v>6706309</v>
+        <v>6706575</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>121745446</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121974045</v>
+        <v>121974043</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626774</v>
+        <v>626822</v>
       </c>
       <c r="R6" t="n">
-        <v>6706491</v>
+        <v>6706382</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121974044</v>
+        <v>121974046</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626770</v>
+        <v>626774</v>
       </c>
       <c r="R7" t="n">
-        <v>6706475</v>
+        <v>6706525</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121974046</v>
+        <v>121974045</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1408,7 +1408,7 @@
         <v>626774</v>
       </c>
       <c r="R8" t="n">
-        <v>6706525</v>
+        <v>6706491</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1468,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121974043</v>
+        <v>121974044</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626822</v>
+        <v>626770</v>
       </c>
       <c r="R9" t="n">
-        <v>6706382</v>
+        <v>6706475</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121974046</v>
+        <v>121974044</v>
       </c>
       <c r="B5" t="n">
         <v>98175</v>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626774</v>
+        <v>626770</v>
       </c>
       <c r="R5" t="n">
-        <v>6706525</v>
+        <v>6706475</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121974043</v>
+        <v>121974046</v>
       </c>
       <c r="B6" t="n">
         <v>98175</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626822</v>
+        <v>626774</v>
       </c>
       <c r="R6" t="n">
-        <v>6706382</v>
+        <v>6706525</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121974044</v>
+        <v>121974043</v>
       </c>
       <c r="B7" t="n">
         <v>98175</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626770</v>
+        <v>626822</v>
       </c>
       <c r="R7" t="n">
-        <v>6706475</v>
+        <v>6706382</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121974044</v>
+        <v>121974045</v>
       </c>
       <c r="B5" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626770</v>
+        <v>626774</v>
       </c>
       <c r="R5" t="n">
-        <v>6706475</v>
+        <v>6706491</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1112,7 +1112,7 @@
         <v>121974046</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121974043</v>
+        <v>121974044</v>
       </c>
       <c r="B7" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626822</v>
+        <v>626770</v>
       </c>
       <c r="R7" t="n">
-        <v>6706382</v>
+        <v>6706475</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121974045</v>
+        <v>121974043</v>
       </c>
       <c r="B8" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626774</v>
+        <v>626822</v>
       </c>
       <c r="R8" t="n">
-        <v>6706491</v>
+        <v>6706382</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121974045</v>
+        <v>121974046</v>
       </c>
       <c r="B5" t="n">
         <v>98185</v>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1049,7 +1049,7 @@
         <v>626774</v>
       </c>
       <c r="R5" t="n">
-        <v>6706491</v>
+        <v>6706525</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121974046</v>
+        <v>121974044</v>
       </c>
       <c r="B6" t="n">
         <v>98185</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626774</v>
+        <v>626770</v>
       </c>
       <c r="R6" t="n">
-        <v>6706525</v>
+        <v>6706475</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121974044</v>
+        <v>121974045</v>
       </c>
       <c r="B7" t="n">
         <v>98185</v>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626770</v>
+        <v>626774</v>
       </c>
       <c r="R7" t="n">
-        <v>6706475</v>
+        <v>6706491</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121974046</v>
+        <v>121974044</v>
       </c>
       <c r="B5" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626774</v>
+        <v>626770</v>
       </c>
       <c r="R5" t="n">
-        <v>6706525</v>
+        <v>6706475</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121974044</v>
+        <v>121974043</v>
       </c>
       <c r="B6" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626770</v>
+        <v>626822</v>
       </c>
       <c r="R6" t="n">
-        <v>6706475</v>
+        <v>6706382</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121974045</v>
+        <v>121974046</v>
       </c>
       <c r="B7" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1287,7 +1287,7 @@
         <v>626774</v>
       </c>
       <c r="R7" t="n">
-        <v>6706491</v>
+        <v>6706525</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121974043</v>
+        <v>121974045</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626822</v>
+        <v>626774</v>
       </c>
       <c r="R8" t="n">
-        <v>6706382</v>
+        <v>6706491</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,6 +1464,342 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122887419</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626811</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6706393</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122887443</v>
+      </c>
+      <c r="B10" t="n">
+        <v>95901</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>53</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>626837</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6706391</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122882064</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>626752</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6706500</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122887443</v>
+        <v>122882064</v>
       </c>
       <c r="B10" t="n">
-        <v>95901</v>
+        <v>98355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,25 +1590,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626837</v>
+        <v>626752</v>
       </c>
       <c r="R10" t="n">
-        <v>6706391</v>
+        <v>6706500</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122882064</v>
+        <v>122887443</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>95901</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,25 +1702,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626752</v>
+        <v>626837</v>
       </c>
       <c r="R11" t="n">
-        <v>6706500</v>
+        <v>6706391</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>122887419</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>122882064</v>
       </c>
       <c r="B10" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>122887443</v>
       </c>
       <c r="B11" t="n">
-        <v>95901</v>
+        <v>95903</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122887419</v>
+        <v>122887443</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>95903</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,25 +1478,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626811</v>
+        <v>626837</v>
       </c>
       <c r="R9" t="n">
-        <v>6706393</v>
+        <v>6706391</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122882064</v>
+        <v>122887419</v>
       </c>
       <c r="B10" t="n">
         <v>98357</v>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626752</v>
+        <v>626811</v>
       </c>
       <c r="R10" t="n">
-        <v>6706500</v>
+        <v>6706393</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122887443</v>
+        <v>122882064</v>
       </c>
       <c r="B11" t="n">
-        <v>95903</v>
+        <v>98357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,25 +1702,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626837</v>
+        <v>626752</v>
       </c>
       <c r="R11" t="n">
-        <v>6706391</v>
+        <v>6706500</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122887443</v>
+        <v>122887419</v>
       </c>
       <c r="B9" t="n">
-        <v>95903</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,25 +1478,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626837</v>
+        <v>626811</v>
       </c>
       <c r="R9" t="n">
-        <v>6706391</v>
+        <v>6706393</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122887419</v>
+        <v>122887443</v>
       </c>
       <c r="B10" t="n">
-        <v>98357</v>
+        <v>95911</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,25 +1590,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626811</v>
+        <v>626837</v>
       </c>
       <c r="R10" t="n">
-        <v>6706393</v>
+        <v>6706391</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1693,7 +1693,7 @@
         <v>122882064</v>
       </c>
       <c r="B11" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122887419</v>
+        <v>122887443</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>95911</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,25 +1478,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626811</v>
+        <v>626837</v>
       </c>
       <c r="R9" t="n">
-        <v>6706393</v>
+        <v>6706391</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122887443</v>
+        <v>122882064</v>
       </c>
       <c r="B10" t="n">
-        <v>95911</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,25 +1590,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626837</v>
+        <v>626752</v>
       </c>
       <c r="R10" t="n">
-        <v>6706391</v>
+        <v>6706500</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,7 +1690,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122882064</v>
+        <v>122887419</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626752</v>
+        <v>626811</v>
       </c>
       <c r="R11" t="n">
-        <v>6706500</v>
+        <v>6706393</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122887443</v>
+        <v>122882064</v>
       </c>
       <c r="B9" t="n">
-        <v>95911</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,25 +1478,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626837</v>
+        <v>626752</v>
       </c>
       <c r="R9" t="n">
-        <v>6706391</v>
+        <v>6706500</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122882064</v>
+        <v>122887443</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>95911</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,25 +1590,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626752</v>
+        <v>626837</v>
       </c>
       <c r="R10" t="n">
-        <v>6706500</v>
+        <v>6706391</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122882064</v>
+        <v>122887443</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>95914</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,25 +1478,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626752</v>
+        <v>626837</v>
       </c>
       <c r="R9" t="n">
-        <v>6706500</v>
+        <v>6706391</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122887443</v>
+        <v>122882064</v>
       </c>
       <c r="B10" t="n">
-        <v>95911</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,25 +1590,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626837</v>
+        <v>626752</v>
       </c>
       <c r="R10" t="n">
-        <v>6706391</v>
+        <v>6706500</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1693,7 @@
         <v>122887419</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122887443</v>
+        <v>122887419</v>
       </c>
       <c r="B9" t="n">
-        <v>95914</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,25 +1478,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626837</v>
+        <v>626811</v>
       </c>
       <c r="R9" t="n">
-        <v>6706391</v>
+        <v>6706393</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122882064</v>
+        <v>122887443</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>95916</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,25 +1590,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626752</v>
+        <v>626837</v>
       </c>
       <c r="R10" t="n">
-        <v>6706500</v>
+        <v>6706391</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122887419</v>
+        <v>122882064</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626811</v>
+        <v>626752</v>
       </c>
       <c r="R11" t="n">
-        <v>6706393</v>
+        <v>6706500</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>122887419</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122887443</v>
+        <v>122882064</v>
       </c>
       <c r="B10" t="n">
-        <v>95916</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,25 +1590,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626837</v>
+        <v>626752</v>
       </c>
       <c r="R10" t="n">
-        <v>6706391</v>
+        <v>6706500</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122882064</v>
+        <v>122887443</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>95922</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,25 +1702,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626752</v>
+        <v>626837</v>
       </c>
       <c r="R11" t="n">
-        <v>6706500</v>
+        <v>6706391</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1800,6 +1800,1397 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126311046</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>626814</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6706319</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126311971</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>626759</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6706687</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126310434</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91291</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>626782</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6706308</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126310827</v>
+      </c>
+      <c r="B15" t="n">
+        <v>9406</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>105076</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Noshornsoxe</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sinodendron cylindricum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>626776</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6706294</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126311872</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>626767</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6706716</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126311108</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96598</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>53</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>626806</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6706334</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126311234</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98379</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>626827</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6706353</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126311186</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>626806</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6706334</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126311894</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95794</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>210</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>626767</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6706716</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126310997</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91657</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>626816</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6706325</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126311942</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>626767</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6706682</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126311950</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>626764</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6706687</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126310071</v>
+      </c>
+      <c r="B24" t="n">
+        <v>96598</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>53</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>626762</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6706408</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>126311046</v>
       </c>
       <c r="B12" t="n">
-        <v>91867</v>
+        <v>91871</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>126311971</v>
       </c>
       <c r="B13" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>126310434</v>
       </c>
       <c r="B14" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,32 +2123,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126310827</v>
+        <v>126311872</v>
       </c>
       <c r="B15" t="n">
-        <v>9406</v>
+        <v>98349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105076</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sinodendron cylindricum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626776</v>
+        <v>626767</v>
       </c>
       <c r="R15" t="n">
-        <v>6706294</v>
+        <v>6706716</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,32 +2230,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126311872</v>
+        <v>126311108</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>96602</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626767</v>
+        <v>626806</v>
       </c>
       <c r="R16" t="n">
-        <v>6706716</v>
+        <v>6706334</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,32 +2337,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126311108</v>
+        <v>126311234</v>
       </c>
       <c r="B17" t="n">
-        <v>96598</v>
+        <v>98383</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626806</v>
+        <v>626827</v>
       </c>
       <c r="R17" t="n">
-        <v>6706334</v>
+        <v>6706353</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2444,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126311234</v>
+        <v>126311186</v>
       </c>
       <c r="B18" t="n">
-        <v>98379</v>
+        <v>5176</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626827</v>
+        <v>626806</v>
       </c>
       <c r="R18" t="n">
-        <v>6706353</v>
+        <v>6706334</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,10 +2551,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126311186</v>
+        <v>126311894</v>
       </c>
       <c r="B19" t="n">
-        <v>5176</v>
+        <v>95798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,21 +2562,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626806</v>
+        <v>626767</v>
       </c>
       <c r="R19" t="n">
-        <v>6706334</v>
+        <v>6706716</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126311894</v>
+        <v>126310997</v>
       </c>
       <c r="B20" t="n">
-        <v>95794</v>
+        <v>91661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2669,21 +2669,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626767</v>
+        <v>626816</v>
       </c>
       <c r="R20" t="n">
-        <v>6706716</v>
+        <v>6706325</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126310997</v>
+        <v>126311942</v>
       </c>
       <c r="B21" t="n">
-        <v>91657</v>
+        <v>98349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626816</v>
+        <v>626767</v>
       </c>
       <c r="R21" t="n">
-        <v>6706325</v>
+        <v>6706682</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2872,10 +2872,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126311942</v>
+        <v>126311950</v>
       </c>
       <c r="B22" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626767</v>
+        <v>626764</v>
       </c>
       <c r="R22" t="n">
-        <v>6706682</v>
+        <v>6706687</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2979,32 +2979,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126311950</v>
+        <v>126310071</v>
       </c>
       <c r="B23" t="n">
-        <v>98345</v>
+        <v>96602</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626764</v>
+        <v>626762</v>
       </c>
       <c r="R23" t="n">
-        <v>6706687</v>
+        <v>6706408</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3086,32 +3086,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126310071</v>
+        <v>126310827</v>
       </c>
       <c r="B24" t="n">
-        <v>96598</v>
+        <v>9406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>105076</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sinodendron cylindricum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626762</v>
+        <v>626776</v>
       </c>
       <c r="R24" t="n">
-        <v>6706408</v>
+        <v>6706294</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -2123,32 +2123,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126311872</v>
+        <v>126311108</v>
       </c>
       <c r="B15" t="n">
-        <v>98349</v>
+        <v>96602</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626767</v>
+        <v>626806</v>
       </c>
       <c r="R15" t="n">
-        <v>6706716</v>
+        <v>6706334</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,32 +2230,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126311108</v>
+        <v>126311872</v>
       </c>
       <c r="B16" t="n">
-        <v>96602</v>
+        <v>98349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626806</v>
+        <v>626767</v>
       </c>
       <c r="R16" t="n">
-        <v>6706334</v>
+        <v>6706716</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -1912,7 +1912,7 @@
         <v>126311971</v>
       </c>
       <c r="B13" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>126311108</v>
       </c>
       <c r="B15" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>126311872</v>
       </c>
       <c r="B16" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>126311234</v>
       </c>
       <c r="B17" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126311894</v>
       </c>
       <c r="B19" t="n">
-        <v>95798</v>
+        <v>95801</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>126311942</v>
       </c>
       <c r="B21" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>126311950</v>
       </c>
       <c r="B22" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>126310071</v>
       </c>
       <c r="B23" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -2658,32 +2658,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126310997</v>
+        <v>126311942</v>
       </c>
       <c r="B20" t="n">
-        <v>91661</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626816</v>
+        <v>626767</v>
       </c>
       <c r="R20" t="n">
-        <v>6706325</v>
+        <v>6706682</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126311942</v>
+        <v>126310997</v>
       </c>
       <c r="B21" t="n">
-        <v>98352</v>
+        <v>91661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626767</v>
+        <v>626816</v>
       </c>
       <c r="R21" t="n">
-        <v>6706682</v>
+        <v>6706325</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -2123,32 +2123,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126311108</v>
+        <v>126311872</v>
       </c>
       <c r="B15" t="n">
-        <v>96605</v>
+        <v>98352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626806</v>
+        <v>626767</v>
       </c>
       <c r="R15" t="n">
-        <v>6706334</v>
+        <v>6706716</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,32 +2230,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126311872</v>
+        <v>126311108</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>96605</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626767</v>
+        <v>626806</v>
       </c>
       <c r="R16" t="n">
-        <v>6706716</v>
+        <v>6706334</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,10 +2337,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126311234</v>
+        <v>126311186</v>
       </c>
       <c r="B17" t="n">
-        <v>98386</v>
+        <v>5176</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626827</v>
+        <v>626806</v>
       </c>
       <c r="R17" t="n">
-        <v>6706353</v>
+        <v>6706334</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2444,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126311186</v>
+        <v>126311234</v>
       </c>
       <c r="B18" t="n">
-        <v>5176</v>
+        <v>98386</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>219874</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626806</v>
+        <v>626827</v>
       </c>
       <c r="R18" t="n">
-        <v>6706334</v>
+        <v>6706353</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,32 +2658,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126311942</v>
+        <v>126310997</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>91661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626767</v>
+        <v>626816</v>
       </c>
       <c r="R20" t="n">
-        <v>6706682</v>
+        <v>6706325</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126310997</v>
+        <v>126311942</v>
       </c>
       <c r="B21" t="n">
-        <v>91661</v>
+        <v>98352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626816</v>
+        <v>626767</v>
       </c>
       <c r="R21" t="n">
-        <v>6706325</v>
+        <v>6706682</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>126311046</v>
       </c>
       <c r="B12" t="n">
-        <v>91871</v>
+        <v>91874</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>126311971</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>126310434</v>
       </c>
       <c r="B14" t="n">
-        <v>91295</v>
+        <v>91298</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>126311872</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>126311108</v>
       </c>
       <c r="B16" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>126311234</v>
       </c>
       <c r="B18" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>126311894</v>
       </c>
       <c r="B19" t="n">
-        <v>95801</v>
+        <v>95810</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2658,32 +2658,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126311942</v>
+        <v>126310997</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>91664</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626767</v>
+        <v>626816</v>
       </c>
       <c r="R20" t="n">
-        <v>6706682</v>
+        <v>6706325</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126310997</v>
+        <v>126311942</v>
       </c>
       <c r="B21" t="n">
-        <v>91661</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626816</v>
+        <v>626767</v>
       </c>
       <c r="R21" t="n">
-        <v>6706325</v>
+        <v>6706682</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2875,7 +2875,7 @@
         <v>126311950</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>126310071</v>
       </c>
       <c r="B23" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -2123,32 +2123,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126311872</v>
+        <v>126311108</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>96614</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626767</v>
+        <v>626806</v>
       </c>
       <c r="R15" t="n">
-        <v>6706716</v>
+        <v>6706334</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,32 +2230,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126311108</v>
+        <v>126311872</v>
       </c>
       <c r="B16" t="n">
-        <v>96614</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626806</v>
+        <v>626767</v>
       </c>
       <c r="R16" t="n">
-        <v>6706334</v>
+        <v>6706716</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -2123,32 +2123,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126311108</v>
+        <v>126311872</v>
       </c>
       <c r="B15" t="n">
-        <v>96614</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626806</v>
+        <v>626767</v>
       </c>
       <c r="R15" t="n">
-        <v>6706334</v>
+        <v>6706716</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,32 +2230,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126311872</v>
+        <v>126311108</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>96614</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626767</v>
+        <v>626806</v>
       </c>
       <c r="R16" t="n">
-        <v>6706716</v>
+        <v>6706334</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,10 +2337,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126311186</v>
+        <v>126311234</v>
       </c>
       <c r="B17" t="n">
-        <v>5176</v>
+        <v>98395</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>219874</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626806</v>
+        <v>626827</v>
       </c>
       <c r="R17" t="n">
-        <v>6706334</v>
+        <v>6706353</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2444,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126311234</v>
+        <v>126311186</v>
       </c>
       <c r="B18" t="n">
-        <v>98395</v>
+        <v>5176</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626827</v>
+        <v>626806</v>
       </c>
       <c r="R18" t="n">
-        <v>6706353</v>
+        <v>6706334</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,32 +2658,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126310997</v>
+        <v>126311942</v>
       </c>
       <c r="B20" t="n">
-        <v>91664</v>
+        <v>98361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626816</v>
+        <v>626767</v>
       </c>
       <c r="R20" t="n">
-        <v>6706325</v>
+        <v>6706682</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126311942</v>
+        <v>126310997</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>91664</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626767</v>
+        <v>626816</v>
       </c>
       <c r="R21" t="n">
-        <v>6706682</v>
+        <v>6706325</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -2658,32 +2658,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126311942</v>
+        <v>126310997</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>91664</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626767</v>
+        <v>626816</v>
       </c>
       <c r="R20" t="n">
-        <v>6706682</v>
+        <v>6706325</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126310997</v>
+        <v>126311942</v>
       </c>
       <c r="B21" t="n">
-        <v>91664</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626816</v>
+        <v>626767</v>
       </c>
       <c r="R21" t="n">
-        <v>6706325</v>
+        <v>6706682</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 55567-2024 artfynd.xlsx
+++ b/artfynd/A 55567-2024 artfynd.xlsx
@@ -2658,32 +2658,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126310997</v>
+        <v>126311942</v>
       </c>
       <c r="B20" t="n">
-        <v>91664</v>
+        <v>98361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626816</v>
+        <v>626767</v>
       </c>
       <c r="R20" t="n">
-        <v>6706325</v>
+        <v>6706682</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,32 +2765,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126311942</v>
+        <v>126310997</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>91664</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626767</v>
+        <v>626816</v>
       </c>
       <c r="R21" t="n">
-        <v>6706682</v>
+        <v>6706325</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
